--- a/docs/AlloQuant_master_CSV_data_dictionary_v7r2.xlsx
+++ b/docs/AlloQuant_master_CSV_data_dictionary_v7r2.xlsx
@@ -565,6 +565,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -614,6 +615,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
@@ -2414,7 +2416,7 @@
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Min side-chain distance K105 to E121 (component of the beta3 Lys / alphaC Glu network).</t>
+          <t>Min side-chain distance between residues at Pfam Pkinase HMM node 62 (PKA canonical K105 position; GLN65 in CSK domain numbering) and HMM node 78 (PKA canonical E121 position; GLU82 in CSK domain numbering). Part of the alphaC-beta4 loop contact network. NOT the beta3-Lys/alphaC-Glu regulatory salt bridge -- for that, see SB_Dist.</t>
         </is>
       </c>
     </row>
